--- a/Esculturas Preço 2022.xlsx
+++ b/Esculturas Preço 2022.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55219\Desktop\www Humberto Escultor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Betinho\Trabalhos\Bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3A52A4-E2E1-41B5-B6B4-AC75EF8EBBFF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98E23D1-2265-4602-AA4C-2F03EDBC493D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="1575" windowWidth="18390" windowHeight="9225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="94">
   <si>
     <t>Obra</t>
   </si>
@@ -1079,6 +1079,9 @@
     <xf numFmtId="164" fontId="23" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1173,9 +1176,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1945,7 +1945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA1FDA3-5984-42AD-9D78-3C441002C09F}">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -1962,23 +1962,23 @@
       <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="114" t="s">
+      <c r="B1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="114"/>
+      <c r="C1" s="115"/>
       <c r="D1" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="115">
+      <c r="F1" s="116">
         <v>2022</v>
       </c>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
     </row>
     <row r="2" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="104" t="s">
@@ -1996,17 +1996,17 @@
       <c r="F2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="116" t="s">
+      <c r="G2" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="117" t="s">
+      <c r="H2" s="117"/>
+      <c r="I2" s="118" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="3" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="104" t="s">
@@ -2024,17 +2024,17 @@
       <c r="F3" s="80">
         <v>300</v>
       </c>
-      <c r="G3" s="118">
+      <c r="G3" s="119">
         <v>100</v>
       </c>
-      <c r="H3" s="118"/>
-      <c r="I3" s="119" t="s">
+      <c r="H3" s="119"/>
+      <c r="I3" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
     </row>
     <row r="4" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="109" t="s">
@@ -2126,7 +2126,7 @@
       <c r="D6" s="105">
         <v>4600</v>
       </c>
-      <c r="F6" s="146" t="s">
+      <c r="F6" s="114" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="84">
@@ -2143,11 +2143,11 @@
         <v>2500</v>
       </c>
       <c r="K6" s="85">
-        <f t="shared" ref="K6:K19" si="0">J6*40/100</f>
+        <f t="shared" ref="K6:K20" si="0">J6*40/100</f>
         <v>1000</v>
       </c>
       <c r="L6" s="85">
-        <f t="shared" ref="L6:L20" si="1">J6*5/3</f>
+        <f t="shared" ref="L6:L21" si="1">J6*5/3</f>
         <v>4166.666666666667</v>
       </c>
       <c r="M6" s="85">
@@ -2266,11 +2266,11 @@
         <v>2800</v>
       </c>
       <c r="K9" s="100">
-        <f t="shared" si="0"/>
+        <f>J9*40/100</f>
         <v>1120</v>
       </c>
       <c r="L9" s="85">
-        <f t="shared" si="1"/>
+        <f>J9*5/3</f>
         <v>4666.666666666667</v>
       </c>
       <c r="M9" s="100">
@@ -2278,43 +2278,43 @@
       </c>
     </row>
     <row r="10" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="110">
         <v>12.8</v>
       </c>
-      <c r="C10" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="105">
+      <c r="C10" s="110" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="111">
         <v>6500</v>
       </c>
-      <c r="F10" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="86">
+      <c r="F10" s="84" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="101">
         <v>11</v>
       </c>
-      <c r="H10" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="87">
-        <f>IF(I10="Granito",G3+G10*F3,G10*F3)</f>
-        <v>3400</v>
-      </c>
-      <c r="K10" s="87">
-        <f t="shared" si="0"/>
-        <v>1360</v>
-      </c>
-      <c r="L10" s="87">
-        <f t="shared" si="1"/>
-        <v>5666.666666666667</v>
-      </c>
-      <c r="M10" s="87">
+      <c r="H10" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="100">
+        <f>IF(I10="Granito",G4+G10*F3,G10*F3)</f>
+        <v>3300</v>
+      </c>
+      <c r="K10" s="100">
+        <f>J10*40/100</f>
+        <v>1320</v>
+      </c>
+      <c r="L10" s="85">
+        <f>J10*5/3</f>
+        <v>5500</v>
+      </c>
+      <c r="M10" s="100">
         <v>5500</v>
       </c>
     </row>
@@ -2332,10 +2332,10 @@
         <v>7000</v>
       </c>
       <c r="F11" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="86">
         <v>11</v>
-      </c>
-      <c r="G11" s="86">
-        <v>11.5</v>
       </c>
       <c r="H11" s="86" t="s">
         <v>23</v>
@@ -2344,19 +2344,19 @@
         <v>31</v>
       </c>
       <c r="J11" s="87">
-        <f>IF(I5="Granito",G3+G11*F3,G11*F3)</f>
-        <v>3450</v>
+        <f>IF(I11="Granito",G3+G11*F3,G11*F3)</f>
+        <v>3400</v>
       </c>
       <c r="K11" s="87">
         <f t="shared" si="0"/>
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="L11" s="87">
         <f t="shared" si="1"/>
-        <v>5750</v>
+        <v>5666.666666666667</v>
       </c>
       <c r="M11" s="87">
-        <v>4000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
@@ -2372,32 +2372,32 @@
       <c r="D12" s="111">
         <v>7500</v>
       </c>
-      <c r="F12" s="84" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="84">
-        <v>12.8</v>
-      </c>
-      <c r="H12" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="84" t="s">
+      <c r="F12" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="86">
+        <v>11.5</v>
+      </c>
+      <c r="H12" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="85">
-        <f>IF(I12="Granito",G3+G12*F3,G12*F3)</f>
-        <v>3940</v>
-      </c>
-      <c r="K12" s="85">
+      <c r="J12" s="87">
+        <f>IF(I5="Granito",G3+G12*F3,G12*F3)</f>
+        <v>3450</v>
+      </c>
+      <c r="K12" s="87">
         <f t="shared" si="0"/>
-        <v>1576</v>
-      </c>
-      <c r="L12" s="85">
+        <v>1380</v>
+      </c>
+      <c r="L12" s="87">
         <f t="shared" si="1"/>
-        <v>6566.666666666667</v>
-      </c>
-      <c r="M12" s="85">
-        <v>6500</v>
+        <v>5750</v>
+      </c>
+      <c r="M12" s="87">
+        <v>4000</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
@@ -2414,31 +2414,31 @@
         <v>7500</v>
       </c>
       <c r="F13" s="84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="84">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="H13" s="84" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J13" s="85">
         <f>IF(I13="Granito",G3+G13*F3,G13*F3)</f>
-        <v>4200</v>
+        <v>3940</v>
       </c>
       <c r="K13" s="85">
         <f t="shared" si="0"/>
-        <v>1680</v>
+        <v>1576</v>
       </c>
       <c r="L13" s="85">
         <f t="shared" si="1"/>
-        <v>7000</v>
+        <v>6566.666666666667</v>
       </c>
       <c r="M13" s="85">
-        <v>7000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
@@ -2454,32 +2454,32 @@
       <c r="D14" s="105">
         <v>8000</v>
       </c>
-      <c r="F14" s="86" t="s">
+      <c r="F14" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="84">
         <v>14</v>
       </c>
-      <c r="G14" s="86">
-        <v>15</v>
-      </c>
-      <c r="H14" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="86" t="s">
+      <c r="H14" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="87">
+      <c r="J14" s="85">
         <f>IF(I14="Granito",G3+G14*F3,G14*F3)</f>
-        <v>4500</v>
-      </c>
-      <c r="K14" s="87">
+        <v>4200</v>
+      </c>
+      <c r="K14" s="85">
         <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-      <c r="L14" s="87">
+        <v>1680</v>
+      </c>
+      <c r="L14" s="85">
         <f t="shared" si="1"/>
-        <v>7500</v>
-      </c>
-      <c r="M14" s="87">
-        <v>7500</v>
+        <v>7000</v>
+      </c>
+      <c r="M14" s="85">
+        <v>7000</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
@@ -2496,7 +2496,7 @@
         <v>11000</v>
       </c>
       <c r="F15" s="86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15" s="86">
         <v>15</v>
@@ -2508,7 +2508,7 @@
         <v>32</v>
       </c>
       <c r="J15" s="87">
-        <f>IF(I14="Granito",G3+G15*F3,G15*F3)</f>
+        <f>IF(I15="Granito",G3+G15*F3,G15*F3)</f>
         <v>4500</v>
       </c>
       <c r="K15" s="87">
@@ -2536,32 +2536,32 @@
       <c r="D16" s="111">
         <v>11100</v>
       </c>
-      <c r="F16" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="84">
-        <v>16</v>
-      </c>
-      <c r="H16" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="84" t="s">
+      <c r="F16" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="86">
+        <v>15</v>
+      </c>
+      <c r="H16" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="85">
-        <f>IF(I16="Granito",G3+G16*F3,G16*F3)</f>
-        <v>4800</v>
-      </c>
-      <c r="K16" s="85">
+      <c r="J16" s="87">
+        <f>IF(I15="Granito",G3+G16*F3,G16*F3)</f>
+        <v>4500</v>
+      </c>
+      <c r="K16" s="87">
         <f t="shared" si="0"/>
-        <v>1920</v>
-      </c>
-      <c r="L16" s="85">
+        <v>1800</v>
+      </c>
+      <c r="L16" s="87">
         <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="M16" s="85">
-        <v>8000</v>
+        <v>7500</v>
+      </c>
+      <c r="M16" s="87">
+        <v>7500</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
@@ -2578,10 +2578,10 @@
         <v>12600</v>
       </c>
       <c r="F17" s="84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" s="84">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H17" s="84" t="s">
         <v>23</v>
@@ -2591,18 +2591,18 @@
       </c>
       <c r="J17" s="85">
         <f>IF(I17="Granito",G3+G17*F3,G17*F3)</f>
-        <v>6600</v>
+        <v>4800</v>
       </c>
       <c r="K17" s="85">
         <f t="shared" si="0"/>
-        <v>2640</v>
+        <v>1920</v>
       </c>
       <c r="L17" s="85">
         <f t="shared" si="1"/>
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="M17" s="85">
-        <v>11000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -2618,32 +2618,32 @@
       <c r="D18" s="108">
         <v>17500</v>
       </c>
-      <c r="F18" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="86">
+      <c r="F18" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="84">
         <v>22</v>
       </c>
-      <c r="H18" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="87">
+      <c r="H18" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="85">
         <f>IF(I18="Granito",G3+G18*F3,G18*F3)</f>
-        <v>6700</v>
-      </c>
-      <c r="K18" s="87">
+        <v>6600</v>
+      </c>
+      <c r="K18" s="85">
         <f t="shared" si="0"/>
-        <v>2680</v>
-      </c>
-      <c r="L18" s="87">
+        <v>2640</v>
+      </c>
+      <c r="L18" s="85">
         <f t="shared" si="1"/>
-        <v>11166.666666666666</v>
-      </c>
-      <c r="M18" s="87">
-        <v>11100</v>
+        <v>11000</v>
+      </c>
+      <c r="M18" s="85">
+        <v>11000</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
@@ -2652,10 +2652,10 @@
       <c r="C19" s="103"/>
       <c r="D19" s="103"/>
       <c r="F19" s="86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G19" s="86">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H19" s="86" t="s">
         <v>23</v>
@@ -2664,19 +2664,19 @@
         <v>31</v>
       </c>
       <c r="J19" s="87">
-        <f>IF(I18="Granito",G3+G19*F3,G19*F3)</f>
-        <v>7600</v>
+        <f>IF(I19="Granito",G3+G19*F3,G19*F3)</f>
+        <v>6700</v>
       </c>
       <c r="K19" s="87">
         <f t="shared" si="0"/>
-        <v>3040</v>
+        <v>2680</v>
       </c>
       <c r="L19" s="87">
         <f t="shared" si="1"/>
-        <v>12666.666666666666</v>
+        <v>11166.666666666666</v>
       </c>
       <c r="M19" s="87">
-        <v>12600</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
@@ -2684,31 +2684,60 @@
       <c r="B20" s="103"/>
       <c r="C20" s="103"/>
       <c r="D20" s="103"/>
-      <c r="F20" s="84" t="s">
+      <c r="F20" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="86">
+        <v>25</v>
+      </c>
+      <c r="H20" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="87">
+        <f>IF(I19="Granito",G3+G20*F3,G20*F3)</f>
+        <v>7600</v>
+      </c>
+      <c r="K20" s="87">
+        <f t="shared" si="0"/>
+        <v>3040</v>
+      </c>
+      <c r="L20" s="87">
+        <f t="shared" si="1"/>
+        <v>12666.666666666666</v>
+      </c>
+      <c r="M20" s="87">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="F21" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="84">
+      <c r="G21" s="84">
         <v>35</v>
       </c>
-      <c r="H20" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="84" t="s">
+      <c r="H21" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="85">
-        <f>IF(I20="Granito",G3+G20*F3,G20*F3)</f>
+      <c r="J21" s="85">
+        <f>IF(I21="Granito",G3+G21*F3,G21*F3)</f>
         <v>10500</v>
       </c>
-      <c r="K20" s="85">
-        <f>J20*40/100</f>
+      <c r="K21" s="85">
+        <f>J21*40/100</f>
         <v>4200</v>
       </c>
-      <c r="L20" s="85">
+      <c r="L21" s="85">
         <f t="shared" si="1"/>
         <v>17500</v>
       </c>
-      <c r="M20" s="85">
+      <c r="M21" s="85">
         <v>17500</v>
       </c>
     </row>
@@ -2742,48 +2771,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="115">
+      <c r="A1" s="116">
         <v>2022</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="117" t="s">
+      <c r="C2" s="117"/>
+      <c r="D2" s="118" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
     </row>
     <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="80">
         <v>300</v>
       </c>
-      <c r="B3" s="118">
+      <c r="B3" s="119">
         <v>100</v>
       </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="119" t="s">
+      <c r="C3" s="119"/>
+      <c r="D3" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="81" t="s">
@@ -3371,53 +3400,53 @@
       <c r="A1" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="116" t="s">
+      <c r="B1" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="117" t="s">
+      <c r="C1" s="117"/>
+      <c r="D1" s="118" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
       <c r="I1" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
     </row>
     <row r="2" spans="1:16" s="79" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80">
         <v>300</v>
       </c>
-      <c r="B2" s="118">
+      <c r="B2" s="119">
         <v>100</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119" t="s">
+      <c r="C2" s="119"/>
+      <c r="D2" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
       <c r="I2" s="80">
         <v>200</v>
       </c>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
     </row>
     <row r="3" spans="1:16" s="79" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="81" t="s">
@@ -3481,9 +3510,9 @@
         <v>1666.6666666666667</v>
       </c>
       <c r="H4" s="85"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
       <c r="L4" s="85"/>
     </row>
     <row r="5" spans="1:16" s="84" customFormat="1" x14ac:dyDescent="0.3">
@@ -4103,15 +4132,15 @@
       <c r="B1" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="124" t="s">
+      <c r="D1" s="125" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="127"/>
       <c r="K1" s="66"/>
       <c r="L1" s="67"/>
       <c r="N1" s="66"/>
@@ -4123,15 +4152,15 @@
       <c r="B2" s="68">
         <v>100</v>
       </c>
-      <c r="D2" s="127" t="s">
+      <c r="D2" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="130"/>
       <c r="K2" s="66"/>
       <c r="L2" s="67"/>
       <c r="N2" s="66"/>
@@ -4951,15 +4980,15 @@
       <c r="A21" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
       <c r="L21" s="37">
         <v>4000</v>
       </c>
@@ -4969,15 +4998,15 @@
       <c r="A22" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="124" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="123"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="123"/>
-      <c r="H22" s="123"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="124"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="124"/>
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
       <c r="K22" s="40"/>
@@ -5058,16 +5087,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -5509,14 +5538,14 @@
       <c r="A19" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="130" t="s">
+      <c r="B19" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
       <c r="H19" s="4">
         <v>4000</v>
       </c>
@@ -5526,14 +5555,14 @@
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="131" t="s">
+      <c r="B20" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
       <c r="H20" s="6">
         <v>200</v>
       </c>
@@ -5557,15 +5586,15 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="136"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="137"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -5577,15 +5606,15 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="137"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="139"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -5597,15 +5626,15 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="139"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="140"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -5617,15 +5646,15 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B5" s="137"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="139"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="140"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -5637,15 +5666,15 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="137"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="139"/>
+      <c r="B6" s="138"/>
+      <c r="C6" s="139"/>
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="140"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -5657,15 +5686,15 @@
       <c r="T6" s="2"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B7" s="137"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="138"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
-      <c r="J7" s="139"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="140"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -5677,15 +5706,15 @@
       <c r="T7" s="2"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="137"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
-      <c r="J8" s="139"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="140"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -5697,15 +5726,15 @@
       <c r="T8" s="2"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="137"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="139"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="140"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -5717,15 +5746,15 @@
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="137"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
-      <c r="J10" s="139"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="140"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -5737,15 +5766,15 @@
       <c r="T10" s="2"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B11" s="137"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="139"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="140"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -5757,15 +5786,15 @@
       <c r="T11" s="2"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" s="137"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="139"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="140"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -5777,15 +5806,15 @@
       <c r="T12" s="2"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="139"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="140"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -5797,15 +5826,15 @@
       <c r="T13" s="2"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B14" s="137"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="139"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="140"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -5817,15 +5846,15 @@
       <c r="T14" s="2"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B15" s="137"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="139"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="140"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -5837,15 +5866,15 @@
       <c r="T15" s="2"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B16" s="137"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="139"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="139"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="140"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -5857,15 +5886,15 @@
       <c r="T16" s="2"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="137"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="139"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="140"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -5877,15 +5906,15 @@
       <c r="T17" s="2"/>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B18" s="137"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="139"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="140"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -5897,15 +5926,15 @@
       <c r="T18" s="2"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="137"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="138"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="139"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="140"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -5917,15 +5946,15 @@
       <c r="T19" s="2"/>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B20" s="137"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="139"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="140"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -5937,15 +5966,15 @@
       <c r="T20" s="2"/>
     </row>
     <row r="21" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="140"/>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="141"/>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="B21" s="141"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="142"/>
+      <c r="J21" s="143"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -5957,48 +5986,48 @@
       <c r="T21" s="2"/>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="143" t="s">
+      <c r="B23" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="143"/>
-      <c r="D23" s="143"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="143"/>
-      <c r="I23" s="143"/>
-      <c r="J23" s="143"/>
-      <c r="L23" s="143" t="s">
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="144"/>
+      <c r="J23" s="144"/>
+      <c r="L23" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="143"/>
-      <c r="N23" s="143"/>
-      <c r="O23" s="143"/>
-      <c r="P23" s="143"/>
-      <c r="Q23" s="143"/>
-      <c r="R23" s="143"/>
-      <c r="S23" s="143"/>
-      <c r="T23" s="143"/>
+      <c r="M23" s="144"/>
+      <c r="N23" s="144"/>
+      <c r="O23" s="144"/>
+      <c r="P23" s="144"/>
+      <c r="Q23" s="144"/>
+      <c r="R23" s="144"/>
+      <c r="S23" s="144"/>
+      <c r="T23" s="144"/>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B24" s="143"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="143"/>
-      <c r="E24" s="143"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="143"/>
-      <c r="J24" s="143"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="143"/>
-      <c r="N24" s="143"/>
-      <c r="O24" s="143"/>
-      <c r="P24" s="143"/>
-      <c r="Q24" s="143"/>
-      <c r="R24" s="143"/>
-      <c r="S24" s="143"/>
-      <c r="T24" s="143"/>
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="144"/>
+      <c r="J24" s="144"/>
+      <c r="L24" s="144"/>
+      <c r="M24" s="144"/>
+      <c r="N24" s="144"/>
+      <c r="O24" s="144"/>
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144"/>
+      <c r="T24" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6424,30 +6453,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145" t="s">
+      <c r="C2" s="146"/>
+      <c r="D2" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="145"/>
+      <c r="E2" s="146"/>
       <c r="F2" s="10" t="s">
         <v>3</v>
       </c>
@@ -6922,43 +6951,43 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A22" s="144" t="s">
+      <c r="A22" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="144"/>
-      <c r="C22" s="144"/>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="144"/>
-      <c r="I22" s="144"/>
+      <c r="B22" s="145"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="145"/>
+      <c r="F22" s="145"/>
+      <c r="G22" s="145"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="145"/>
     </row>
     <row r="23" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A23" s="144" t="s">
+      <c r="A23" s="145" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="144"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="144"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="145"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="145" t="s">
+      <c r="B24" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="145"/>
-      <c r="D24" s="145" t="s">
+      <c r="C24" s="146"/>
+      <c r="D24" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="145"/>
+      <c r="E24" s="146"/>
       <c r="F24" s="10" t="s">
         <v>3</v>
       </c>

--- a/Esculturas Preço 2022.xlsx
+++ b/Esculturas Preço 2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Betinho\Trabalhos\Bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98E23D1-2265-4602-AA4C-2F03EDBC493D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D6CE43-B4DE-45C8-A469-C6C3527A5519}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="1575" windowWidth="18390" windowHeight="9225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,10 @@
     <sheet name="Balanço 07-2017" sheetId="7" r:id="rId7"/>
     <sheet name="Downtown" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="preçoBase">'2022'!$B$3</definedName>
+    <definedName name="preçoBronze">'2022'!$A$3</definedName>
+  </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="95">
   <si>
     <t>Obra</t>
   </si>
@@ -314,6 +318,9 @@
   </si>
   <si>
     <t>preço Kg antigo</t>
+  </si>
+  <si>
+    <t>preço</t>
   </si>
 </sst>
 </file>
@@ -324,7 +331,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,15 +543,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,12 +590,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +744,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1048,42 +1042,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1176,6 +1136,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1945,812 +1908,938 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA1FDA3-5984-42AD-9D78-3C441002C09F}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
+    <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="104">
+        <v>2022</v>
+      </c>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+    </row>
+    <row r="2" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="105" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="105"/>
+      <c r="D2" s="106" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+    </row>
+    <row r="3" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="80">
+        <v>300</v>
+      </c>
+      <c r="B3" s="107">
+        <v>100</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="108" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+    </row>
+    <row r="4" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="115" t="s">
+      <c r="B4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="113" t="s">
+      <c r="C4" s="81"/>
+      <c r="D4" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="116">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-    </row>
-    <row r="2" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="H4" s="82" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="101">
-        <v>3</v>
-      </c>
-      <c r="C2" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="105">
-        <v>1600</v>
-      </c>
-      <c r="F2" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="117" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="117"/>
-      <c r="I2" s="118" t="s">
-        <v>89</v>
-      </c>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-    </row>
-    <row r="3" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="104" t="s">
+      <c r="B5" s="86">
+        <v>2</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="87">
+        <f>IF(D5="Granito",preçoBase+B5*preçoBronze,B5*preçoBronze)</f>
+        <v>700</v>
+      </c>
+      <c r="F5" s="87">
+        <f t="shared" ref="F5" si="0">E5*40/100</f>
+        <v>280</v>
+      </c>
+      <c r="G5" s="87">
+        <f t="shared" ref="G5" si="1">E5*5/3</f>
+        <v>1166.6666666666667</v>
+      </c>
+      <c r="H5" s="87">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="101">
+      <c r="B6" s="86">
         <v>4.5</v>
       </c>
-      <c r="C3" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="105">
-        <v>2400</v>
-      </c>
-      <c r="F3" s="80">
-        <v>300</v>
-      </c>
-      <c r="G3" s="119">
-        <v>100</v>
-      </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-    </row>
-    <row r="4" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="109" t="s">
+      <c r="C6" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="87">
+        <f>IF(D6="Granito",preçoBase+B6*preçoBronze,B6*preçoBronze)</f>
+        <v>1450</v>
+      </c>
+      <c r="F6" s="87">
+        <f>E6*40/100</f>
+        <v>580</v>
+      </c>
+      <c r="G6" s="87">
+        <f>E6*5/3</f>
+        <v>2416.6666666666665</v>
+      </c>
+      <c r="H6" s="87">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B7" s="84">
         <v>6</v>
       </c>
-      <c r="C4" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="111">
-        <v>3150</v>
-      </c>
-      <c r="F4" s="81" t="s">
+      <c r="C7" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="135">
+        <f>IF(D7="Granito",preçoBase+B7*preçoBronze,B7*preçoBronze)</f>
+        <v>1900</v>
+      </c>
+      <c r="F7" s="85">
+        <f t="shared" ref="F7:F21" si="2">E7*40/100</f>
+        <v>760</v>
+      </c>
+      <c r="G7" s="85">
+        <f t="shared" ref="G7:G22" si="3">E7*5/3</f>
+        <v>3166.6666666666665</v>
+      </c>
+      <c r="H7" s="85">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="84">
+        <v>8</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="135">
+        <f>IF(D8="Granito",preçoBase+B8*preçoBronze,B8*preçoBronze)</f>
+        <v>2500</v>
+      </c>
+      <c r="F8" s="85">
+        <f>E8*40/100</f>
+        <v>1000</v>
+      </c>
+      <c r="G8" s="85">
+        <f>E8*5/3</f>
+        <v>4166.666666666667</v>
+      </c>
+      <c r="H8" s="85">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="86">
+        <v>11</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="87">
+        <f>IF(D9="Granito",preçoBase+B9*preçoBronze,B9*preçoBronze)</f>
+        <v>3300</v>
+      </c>
+      <c r="F9" s="87">
+        <f>E9*40/100</f>
+        <v>1320</v>
+      </c>
+      <c r="G9" s="87">
+        <f>E9*5/3</f>
+        <v>5500</v>
+      </c>
+      <c r="H9" s="87">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="86">
+        <v>9</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="87">
+        <f>IF(D10="Granito",preçoBase+B10*preçoBronze,B10*preçoBronze)</f>
+        <v>2800</v>
+      </c>
+      <c r="F10" s="87">
+        <f>E10*40/100</f>
+        <v>1120</v>
+      </c>
+      <c r="G10" s="87">
+        <f>E10*5/3</f>
+        <v>4666.666666666667</v>
+      </c>
+      <c r="H10" s="87">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="101">
+        <v>11</v>
+      </c>
+      <c r="C11" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="135">
+        <f>IF(D11="Granito",preçoBase+B11*preçoBronze,B11*preçoBronze)</f>
+        <v>3300</v>
+      </c>
+      <c r="F11" s="100">
+        <f>E11*40/100</f>
+        <v>1320</v>
+      </c>
+      <c r="G11" s="85">
+        <f>E11*5/3</f>
+        <v>5500</v>
+      </c>
+      <c r="H11" s="100">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="101">
+        <v>11</v>
+      </c>
+      <c r="C12" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="135">
+        <f>IF(D12="Granito",preçoBase+B12*preçoBronze,B12*preçoBronze)</f>
+        <v>3400</v>
+      </c>
+      <c r="F12" s="100">
+        <f t="shared" si="2"/>
+        <v>1360</v>
+      </c>
+      <c r="G12" s="85">
+        <f t="shared" si="3"/>
+        <v>5666.666666666667</v>
+      </c>
+      <c r="H12" s="100">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="86">
+        <v>11.5</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="87">
+        <f>IF(D13="Granito",preçoBase+B13*preçoBronze,B13*preçoBronze)</f>
+        <v>3550</v>
+      </c>
+      <c r="F13" s="87">
+        <f t="shared" si="2"/>
+        <v>1420</v>
+      </c>
+      <c r="G13" s="87">
+        <f t="shared" si="3"/>
+        <v>5916.666666666667</v>
+      </c>
+      <c r="H13" s="87">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="86">
+        <v>12.8</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="87">
+        <f>IF(D14="Granito",preçoBase+B14*preçoBronze,B14*preçoBronze)</f>
+        <v>3940</v>
+      </c>
+      <c r="F14" s="87">
+        <f t="shared" si="2"/>
+        <v>1576</v>
+      </c>
+      <c r="G14" s="87">
+        <f t="shared" si="3"/>
+        <v>6566.666666666667</v>
+      </c>
+      <c r="H14" s="87">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="84">
+        <v>14</v>
+      </c>
+      <c r="C15" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="135">
+        <f>IF(D15="Granito",preçoBase+B15*preçoBronze,B15*preçoBronze)</f>
+        <v>4200</v>
+      </c>
+      <c r="F15" s="85">
+        <f t="shared" si="2"/>
+        <v>1680</v>
+      </c>
+      <c r="G15" s="85">
+        <f t="shared" si="3"/>
+        <v>7000</v>
+      </c>
+      <c r="H15" s="85">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="101">
+        <v>15</v>
+      </c>
+      <c r="C16" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="135">
+        <f>IF(D16="Granito",preçoBase+B16*preçoBronze,B16*preçoBronze)</f>
+        <v>4500</v>
+      </c>
+      <c r="F16" s="100">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
+      <c r="G16" s="85">
+        <f t="shared" si="3"/>
+        <v>7500</v>
+      </c>
+      <c r="H16" s="100">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="86">
+        <v>15</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="87">
+        <f>IF(D17="Granito",preçoBase+B17*preçoBronze,B17*preçoBronze)</f>
+        <v>4500</v>
+      </c>
+      <c r="F17" s="87">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
+      <c r="G17" s="87">
+        <f t="shared" si="3"/>
+        <v>7500</v>
+      </c>
+      <c r="H17" s="87">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="86">
+        <v>16</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="87">
+        <f>IF(D18="Granito",preçoBase+B18*preçoBronze,B18*preçoBronze)</f>
+        <v>4800</v>
+      </c>
+      <c r="F18" s="87">
+        <f t="shared" si="2"/>
+        <v>1920</v>
+      </c>
+      <c r="G18" s="87">
+        <f t="shared" si="3"/>
+        <v>8000</v>
+      </c>
+      <c r="H18" s="87">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="84">
+        <v>22</v>
+      </c>
+      <c r="C19" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="135">
+        <f>IF(D19="Granito",preçoBase+B19*preçoBronze,B19*preçoBronze)</f>
+        <v>6600</v>
+      </c>
+      <c r="F19" s="85">
+        <f t="shared" si="2"/>
+        <v>2640</v>
+      </c>
+      <c r="G19" s="85">
+        <f t="shared" si="3"/>
+        <v>11000</v>
+      </c>
+      <c r="H19" s="85">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="84">
+        <v>22</v>
+      </c>
+      <c r="C20" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="135">
+        <f>IF(D20="Granito",preçoBase+B20*preçoBronze,B20*preçoBronze)</f>
+        <v>6700</v>
+      </c>
+      <c r="F20" s="85">
+        <f t="shared" si="2"/>
+        <v>2680</v>
+      </c>
+      <c r="G20" s="85">
+        <f t="shared" si="3"/>
+        <v>11166.666666666666</v>
+      </c>
+      <c r="H20" s="85">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="86">
+        <v>25</v>
+      </c>
+      <c r="C21" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="87">
+        <f>IF(D21="Granito",preçoBase+B21*preçoBronze,B21*preçoBronze)</f>
+        <v>7600</v>
+      </c>
+      <c r="F21" s="87">
+        <f t="shared" si="2"/>
+        <v>3040</v>
+      </c>
+      <c r="G21" s="87">
+        <f t="shared" si="3"/>
+        <v>12666.666666666666</v>
+      </c>
+      <c r="H21" s="87">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="86">
+        <v>35</v>
+      </c>
+      <c r="C22" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="87">
+        <f>IF(D22="Granito",preçoBase+B22*preçoBronze,B22*preçoBronze)</f>
+        <v>10500</v>
+      </c>
+      <c r="F22" s="87">
+        <f>E22*40/100</f>
+        <v>4200</v>
+      </c>
+      <c r="G22" s="87">
+        <f t="shared" si="3"/>
+        <v>17500</v>
+      </c>
+      <c r="H22" s="87">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="81" t="s">
+      <c r="B24" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81" t="s">
+      <c r="C24" s="81"/>
+      <c r="D24" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="82" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="109" t="s">
+      <c r="E24" s="82" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="86">
+        <v>2</v>
+      </c>
+      <c r="C25" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="87">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="86">
+        <v>4.5</v>
+      </c>
+      <c r="C26" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="87">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="84">
+        <v>6</v>
+      </c>
+      <c r="C27" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="85">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B28" s="84">
         <v>8</v>
       </c>
-      <c r="C5" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="111">
-        <v>4100</v>
-      </c>
-      <c r="F5" s="84" t="s">
+      <c r="C28" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="85">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="84">
+      <c r="B29" s="86">
         <v>11</v>
       </c>
-      <c r="H5" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="84" t="s">
+      <c r="C29" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="85">
-        <f>IF(I5="Granito",G3+G5*F3,G5*F3)</f>
-        <v>3300</v>
-      </c>
-      <c r="K5" s="85">
-        <f>J5*40/100</f>
-        <v>1320</v>
-      </c>
-      <c r="L5" s="85">
-        <f>J5*5/3</f>
+      <c r="E29" s="87">
         <v>5500</v>
       </c>
-      <c r="M5" s="85">
+    </row>
+    <row r="30" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A30" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="86">
+        <v>9</v>
+      </c>
+      <c r="C30" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="87">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A31" s="84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="101">
+        <v>11</v>
+      </c>
+      <c r="C31" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="100">
         <v>5500</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="101">
-        <v>9</v>
-      </c>
-      <c r="C6" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="105">
-        <v>4600</v>
-      </c>
-      <c r="F6" s="114" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="84">
-        <v>8</v>
-      </c>
-      <c r="H6" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="84" t="s">
+    <row r="32" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A32" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="101">
+        <v>11</v>
+      </c>
+      <c r="C32" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="100">
-        <f>IF(I6="Granito",G3+G6*F3,G6*F3)</f>
-        <v>2500</v>
-      </c>
-      <c r="K6" s="85">
-        <f t="shared" ref="K6:K20" si="0">J6*40/100</f>
-        <v>1000</v>
-      </c>
-      <c r="L6" s="85">
-        <f t="shared" ref="L6:L21" si="1">J6*5/3</f>
-        <v>4166.666666666667</v>
-      </c>
-      <c r="M6" s="85">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="104" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="101">
+      <c r="E32" s="100">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A33" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="105">
-        <v>5500</v>
-      </c>
-      <c r="F7" s="86" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="86">
-        <v>6</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="86" t="s">
+      <c r="B33" s="86">
+        <v>11.5</v>
+      </c>
+      <c r="C33" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="87">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="86">
+        <v>12.8</v>
+      </c>
+      <c r="C34" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="87">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="84">
+        <v>14</v>
+      </c>
+      <c r="C35" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="87">
-        <f>IF(I6="Granito",G3+G7*F3,G7*F3)</f>
-        <v>1900</v>
-      </c>
-      <c r="K7" s="87">
-        <f t="shared" si="0"/>
-        <v>760</v>
-      </c>
-      <c r="L7" s="87">
-        <f t="shared" si="1"/>
-        <v>3166.6666666666665</v>
-      </c>
-      <c r="M7" s="87">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="109" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="110">
-        <v>11</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="111">
-        <v>5500</v>
-      </c>
-      <c r="F8" s="86" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="86">
-        <v>8</v>
-      </c>
-      <c r="H8" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="86" t="s">
+      <c r="E35" s="85">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="101">
+        <v>15</v>
+      </c>
+      <c r="C36" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="100">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="86">
+        <v>15</v>
+      </c>
+      <c r="C37" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="87">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="86">
+        <v>16</v>
+      </c>
+      <c r="C38" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="87">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="84">
+        <v>22</v>
+      </c>
+      <c r="C39" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="85">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="84">
+        <v>22</v>
+      </c>
+      <c r="C40" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="87">
-        <f>IF(I8="Granito",G3+G8*F3,G8*F3)</f>
-        <v>2500</v>
-      </c>
-      <c r="K8" s="87">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="L8" s="87">
-        <f t="shared" si="1"/>
-        <v>4166.666666666667</v>
-      </c>
-      <c r="M8" s="87">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="109" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="110">
-        <v>11.5</v>
-      </c>
-      <c r="C9" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="111">
-        <v>4000</v>
-      </c>
-      <c r="F9" s="84" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="101">
-        <v>9</v>
-      </c>
-      <c r="H9" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="84" t="s">
+      <c r="E40" s="85">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="86">
+        <v>25</v>
+      </c>
+      <c r="C41" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="100">
-        <f>IF(I9="Granito",G3+G9*F3,G9*F3)</f>
-        <v>2800</v>
-      </c>
-      <c r="K9" s="100">
-        <f>J9*40/100</f>
-        <v>1120</v>
-      </c>
-      <c r="L9" s="85">
-        <f>J9*5/3</f>
-        <v>4666.666666666667</v>
-      </c>
-      <c r="M9" s="100">
-        <v>4600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="110">
-        <v>12.8</v>
-      </c>
-      <c r="C10" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="111">
-        <v>6500</v>
-      </c>
-      <c r="F10" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="101">
-        <v>11</v>
-      </c>
-      <c r="H10" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="84" t="s">
+      <c r="E41" s="87">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="86">
+        <v>35</v>
+      </c>
+      <c r="C42" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="100">
-        <f>IF(I10="Granito",G4+G10*F3,G10*F3)</f>
-        <v>3300</v>
-      </c>
-      <c r="K10" s="100">
-        <f>J10*40/100</f>
-        <v>1320</v>
-      </c>
-      <c r="L10" s="85">
-        <f>J10*5/3</f>
-        <v>5500</v>
-      </c>
-      <c r="M10" s="100">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="101">
-        <v>14</v>
-      </c>
-      <c r="C11" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="105">
-        <v>7000</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="86">
-        <v>11</v>
-      </c>
-      <c r="H11" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="87">
-        <f>IF(I11="Granito",G3+G11*F3,G11*F3)</f>
-        <v>3400</v>
-      </c>
-      <c r="K11" s="87">
-        <f t="shared" si="0"/>
-        <v>1360</v>
-      </c>
-      <c r="L11" s="87">
-        <f t="shared" si="1"/>
-        <v>5666.666666666667</v>
-      </c>
-      <c r="M11" s="87">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="110">
-        <v>15</v>
-      </c>
-      <c r="C12" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="111">
-        <v>7500</v>
-      </c>
-      <c r="F12" s="86" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="86">
-        <v>11.5</v>
-      </c>
-      <c r="H12" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="87">
-        <f>IF(I5="Granito",G3+G12*F3,G12*F3)</f>
-        <v>3450</v>
-      </c>
-      <c r="K12" s="87">
-        <f t="shared" si="0"/>
-        <v>1380</v>
-      </c>
-      <c r="L12" s="87">
-        <f t="shared" si="1"/>
-        <v>5750</v>
-      </c>
-      <c r="M12" s="87">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="110">
-        <v>15</v>
-      </c>
-      <c r="C13" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="111">
-        <v>7500</v>
-      </c>
-      <c r="F13" s="84" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="84">
-        <v>12.8</v>
-      </c>
-      <c r="H13" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="84" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="85">
-        <f>IF(I13="Granito",G3+G13*F3,G13*F3)</f>
-        <v>3940</v>
-      </c>
-      <c r="K13" s="85">
-        <f t="shared" si="0"/>
-        <v>1576</v>
-      </c>
-      <c r="L13" s="85">
-        <f t="shared" si="1"/>
-        <v>6566.666666666667</v>
-      </c>
-      <c r="M13" s="85">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="101">
-        <v>16</v>
-      </c>
-      <c r="C14" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="105">
-        <v>8000</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="84">
-        <v>14</v>
-      </c>
-      <c r="H14" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="85">
-        <f>IF(I14="Granito",G3+G14*F3,G14*F3)</f>
-        <v>4200</v>
-      </c>
-      <c r="K14" s="85">
-        <f t="shared" si="0"/>
-        <v>1680</v>
-      </c>
-      <c r="L14" s="85">
-        <f t="shared" si="1"/>
-        <v>7000</v>
-      </c>
-      <c r="M14" s="85">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="104" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="101">
-        <v>22</v>
-      </c>
-      <c r="C15" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="105">
-        <v>11000</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="86">
-        <v>15</v>
-      </c>
-      <c r="H15" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="87">
-        <f>IF(I15="Granito",G3+G15*F3,G15*F3)</f>
-        <v>4500</v>
-      </c>
-      <c r="K15" s="87">
-        <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-      <c r="L15" s="87">
-        <f t="shared" si="1"/>
-        <v>7500</v>
-      </c>
-      <c r="M15" s="87">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="109" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="110">
-        <v>22</v>
-      </c>
-      <c r="C16" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="111">
-        <v>11100</v>
-      </c>
-      <c r="F16" s="86" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="86">
-        <v>15</v>
-      </c>
-      <c r="H16" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="87">
-        <f>IF(I15="Granito",G3+G16*F3,G16*F3)</f>
-        <v>4500</v>
-      </c>
-      <c r="K16" s="87">
-        <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-      <c r="L16" s="87">
-        <f t="shared" si="1"/>
-        <v>7500</v>
-      </c>
-      <c r="M16" s="87">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="109" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="110">
-        <v>25</v>
-      </c>
-      <c r="C17" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="111">
-        <v>12600</v>
-      </c>
-      <c r="F17" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="84">
-        <v>16</v>
-      </c>
-      <c r="H17" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="85">
-        <f>IF(I17="Granito",G3+G17*F3,G17*F3)</f>
-        <v>4800</v>
-      </c>
-      <c r="K17" s="85">
-        <f t="shared" si="0"/>
-        <v>1920</v>
-      </c>
-      <c r="L17" s="85">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="M17" s="85">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="106" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="107">
-        <v>35</v>
-      </c>
-      <c r="C18" s="107" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="108">
+      <c r="E42" s="87">
         <v>17500</v>
       </c>
-      <c r="F18" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="84">
-        <v>22</v>
-      </c>
-      <c r="H18" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="85">
-        <f>IF(I18="Granito",G3+G18*F3,G18*F3)</f>
-        <v>6600</v>
-      </c>
-      <c r="K18" s="85">
-        <f t="shared" si="0"/>
-        <v>2640</v>
-      </c>
-      <c r="L18" s="85">
-        <f t="shared" si="1"/>
-        <v>11000</v>
-      </c>
-      <c r="M18" s="85">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="103"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="F19" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="86">
-        <v>22</v>
-      </c>
-      <c r="H19" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="87">
-        <f>IF(I19="Granito",G3+G19*F3,G19*F3)</f>
-        <v>6700</v>
-      </c>
-      <c r="K19" s="87">
-        <f t="shared" si="0"/>
-        <v>2680</v>
-      </c>
-      <c r="L19" s="87">
-        <f t="shared" si="1"/>
-        <v>11166.666666666666</v>
-      </c>
-      <c r="M19" s="87">
-        <v>11100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="103"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="F20" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="86">
-        <v>25</v>
-      </c>
-      <c r="H20" s="86" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="87">
-        <f>IF(I19="Granito",G3+G20*F3,G20*F3)</f>
-        <v>7600</v>
-      </c>
-      <c r="K20" s="87">
-        <f t="shared" si="0"/>
-        <v>3040</v>
-      </c>
-      <c r="L20" s="87">
-        <f t="shared" si="1"/>
-        <v>12666.666666666666</v>
-      </c>
-      <c r="M20" s="87">
-        <v>12600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="F21" s="84" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="84">
-        <v>35</v>
-      </c>
-      <c r="H21" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="85">
-        <f>IF(I21="Granito",G3+G21*F3,G21*F3)</f>
-        <v>10500</v>
-      </c>
-      <c r="K21" s="85">
-        <f>J21*40/100</f>
-        <v>4200</v>
-      </c>
-      <c r="L21" s="85">
-        <f t="shared" si="1"/>
-        <v>17500</v>
-      </c>
-      <c r="M21" s="85">
-        <v>17500</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:M3"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:H3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2771,48 +2860,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="116">
+      <c r="A1" s="104">
         <v>2022</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
     </row>
     <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118" t="s">
+      <c r="C2" s="105"/>
+      <c r="D2" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
     </row>
     <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="80">
         <v>300</v>
       </c>
-      <c r="B3" s="119">
+      <c r="B3" s="107">
         <v>100</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="120" t="s">
+      <c r="C3" s="107"/>
+      <c r="D3" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="81" t="s">
@@ -3400,53 +3489,53 @@
       <c r="A1" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="117" t="s">
+      <c r="B1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118" t="s">
+      <c r="C1" s="105"/>
+      <c r="D1" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
       <c r="I1" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
     </row>
     <row r="2" spans="1:16" s="79" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80">
         <v>300</v>
       </c>
-      <c r="B2" s="119">
+      <c r="B2" s="107">
         <v>100</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="120" t="s">
+      <c r="C2" s="107"/>
+      <c r="D2" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="80">
         <v>200</v>
       </c>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
     </row>
     <row r="3" spans="1:16" s="79" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="81" t="s">
@@ -3510,9 +3599,9 @@
         <v>1666.6666666666667</v>
       </c>
       <c r="H4" s="85"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
       <c r="L4" s="85"/>
     </row>
     <row r="5" spans="1:16" s="84" customFormat="1" x14ac:dyDescent="0.3">
@@ -4132,15 +4221,15 @@
       <c r="B1" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="125" t="s">
+      <c r="D1" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="127"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="115"/>
       <c r="K1" s="66"/>
       <c r="L1" s="67"/>
       <c r="N1" s="66"/>
@@ -4152,15 +4241,15 @@
       <c r="B2" s="68">
         <v>100</v>
       </c>
-      <c r="D2" s="128" t="s">
+      <c r="D2" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="130"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="118"/>
       <c r="K2" s="66"/>
       <c r="L2" s="67"/>
       <c r="N2" s="66"/>
@@ -4980,15 +5069,15 @@
       <c r="A21" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="123" t="s">
+      <c r="B21" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="123"/>
-      <c r="H21" s="123"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
       <c r="L21" s="37">
         <v>4000</v>
       </c>
@@ -4998,15 +5087,15 @@
       <c r="A22" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="124" t="s">
+      <c r="B22" s="112" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="124"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="124"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
       <c r="K22" s="40"/>
@@ -5087,16 +5176,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -5538,14 +5627,14 @@
       <c r="A19" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="131" t="s">
+      <c r="B19" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="131"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="131"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
       <c r="H19" s="4">
         <v>4000</v>
       </c>
@@ -5555,14 +5644,14 @@
       <c r="A20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="132" t="s">
+      <c r="B20" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="132"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
       <c r="H20" s="6">
         <v>200</v>
       </c>
@@ -5586,15 +5675,15 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="137"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="125"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -5606,15 +5695,15 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="138"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -5626,15 +5715,15 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B4" s="138"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="140"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="128"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -5646,15 +5735,15 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B5" s="138"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="139"/>
-      <c r="J5" s="140"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="128"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -5666,15 +5755,15 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="138"/>
-      <c r="C6" s="139"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="139"/>
-      <c r="J6" s="140"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="128"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -5686,15 +5775,15 @@
       <c r="T6" s="2"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B7" s="138"/>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="140"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -5706,15 +5795,15 @@
       <c r="T7" s="2"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="138"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
-      <c r="F8" s="139"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="140"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="128"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -5726,15 +5815,15 @@
       <c r="T8" s="2"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="138"/>
-      <c r="C9" s="139"/>
-      <c r="D9" s="139"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="140"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="128"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -5746,15 +5835,15 @@
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="138"/>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="140"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="128"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -5766,15 +5855,15 @@
       <c r="T10" s="2"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B11" s="138"/>
-      <c r="C11" s="139"/>
-      <c r="D11" s="139"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="139"/>
-      <c r="G11" s="139"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="140"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="128"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -5786,15 +5875,15 @@
       <c r="T11" s="2"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" s="138"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="140"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="128"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -5806,15 +5895,15 @@
       <c r="T12" s="2"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B13" s="138"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="140"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="128"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -5826,15 +5915,15 @@
       <c r="T13" s="2"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B14" s="138"/>
-      <c r="C14" s="139"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="139"/>
-      <c r="J14" s="140"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="128"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -5846,15 +5935,15 @@
       <c r="T14" s="2"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B15" s="138"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="140"/>
+      <c r="B15" s="126"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="128"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -5866,15 +5955,15 @@
       <c r="T15" s="2"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B16" s="138"/>
-      <c r="C16" s="139"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="139"/>
-      <c r="J16" s="140"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="128"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -5886,15 +5975,15 @@
       <c r="T16" s="2"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="138"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="139"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="139"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="140"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="128"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -5906,15 +5995,15 @@
       <c r="T17" s="2"/>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B18" s="138"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="139"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="140"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="128"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -5926,15 +6015,15 @@
       <c r="T18" s="2"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="138"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="139"/>
-      <c r="I19" s="139"/>
-      <c r="J19" s="140"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="128"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -5946,15 +6035,15 @@
       <c r="T19" s="2"/>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B20" s="138"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="140"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="127"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="127"/>
+      <c r="J20" s="128"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -5966,15 +6055,15 @@
       <c r="T20" s="2"/>
     </row>
     <row r="21" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="141"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="142"/>
-      <c r="G21" s="142"/>
-      <c r="H21" s="142"/>
-      <c r="I21" s="142"/>
-      <c r="J21" s="143"/>
+      <c r="B21" s="129"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="131"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -5986,48 +6075,48 @@
       <c r="T21" s="2"/>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="144" t="s">
+      <c r="B23" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
-      <c r="L23" s="144" t="s">
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="132"/>
+      <c r="L23" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="144"/>
-      <c r="N23" s="144"/>
-      <c r="O23" s="144"/>
-      <c r="P23" s="144"/>
-      <c r="Q23" s="144"/>
-      <c r="R23" s="144"/>
-      <c r="S23" s="144"/>
-      <c r="T23" s="144"/>
+      <c r="M23" s="132"/>
+      <c r="N23" s="132"/>
+      <c r="O23" s="132"/>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="132"/>
+      <c r="R23" s="132"/>
+      <c r="S23" s="132"/>
+      <c r="T23" s="132"/>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="144"/>
-      <c r="J24" s="144"/>
-      <c r="L24" s="144"/>
-      <c r="M24" s="144"/>
-      <c r="N24" s="144"/>
-      <c r="O24" s="144"/>
-      <c r="P24" s="144"/>
-      <c r="Q24" s="144"/>
-      <c r="R24" s="144"/>
-      <c r="S24" s="144"/>
-      <c r="T24" s="144"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="132"/>
+      <c r="L24" s="132"/>
+      <c r="M24" s="132"/>
+      <c r="N24" s="132"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="132"/>
+      <c r="R24" s="132"/>
+      <c r="S24" s="132"/>
+      <c r="T24" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6453,30 +6542,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="133" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146" t="s">
+      <c r="C2" s="134"/>
+      <c r="D2" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="146"/>
+      <c r="E2" s="134"/>
       <c r="F2" s="10" t="s">
         <v>3</v>
       </c>
@@ -6951,43 +7040,43 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A22" s="145" t="s">
+      <c r="A22" s="133" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="145"/>
-      <c r="G22" s="145"/>
-      <c r="H22" s="145"/>
-      <c r="I22" s="145"/>
+      <c r="B22" s="133"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="133"/>
+      <c r="I22" s="133"/>
     </row>
     <row r="23" spans="1:9" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A23" s="145" t="s">
+      <c r="A23" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="145"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="145"/>
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="133"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="146"/>
-      <c r="D24" s="146" t="s">
+      <c r="C24" s="134"/>
+      <c r="D24" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="146"/>
+      <c r="E24" s="134"/>
       <c r="F24" s="10" t="s">
         <v>3</v>
       </c>
